--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/48.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/48.xlsx
@@ -426,13 +426,13 @@
         <v>-10.22452286878376</v>
       </c>
       <c r="E2">
-        <v>-7.33251624687546</v>
+        <v>-4.6693070975425</v>
       </c>
       <c r="F2">
-        <v>-0.5445473402954299</v>
+        <v>-0.2572769803111866</v>
       </c>
       <c r="G2">
-        <v>-8.136275953806502</v>
+        <v>-6.323484116866847</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.880839364687757</v>
       </c>
       <c r="E3">
-        <v>-8.669751978970478</v>
+        <v>-7.07173048572174</v>
       </c>
       <c r="F3">
-        <v>-0.8271175436361889</v>
+        <v>-0.5490221810053529</v>
       </c>
       <c r="G3">
-        <v>-7.338752291213916</v>
+        <v>-5.494761873112169</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.539905224237819</v>
       </c>
       <c r="E4">
-        <v>-9.633669370821167</v>
+        <v>-7.661740835707103</v>
       </c>
       <c r="F4">
-        <v>-0.821497899175597</v>
+        <v>-0.5999626344405085</v>
       </c>
       <c r="G4">
-        <v>-7.654869663667843</v>
+        <v>-6.451092405223593</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.238724310590237</v>
       </c>
       <c r="E5">
-        <v>-9.595680002370822</v>
+        <v>-8.157807992403344</v>
       </c>
       <c r="F5">
-        <v>-0.8454998446717128</v>
+        <v>-0.7329031770787872</v>
       </c>
       <c r="G5">
-        <v>-7.212762859625872</v>
+        <v>-5.262374818437488</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.967243380867806</v>
       </c>
       <c r="E6">
-        <v>-10.05839041952656</v>
+        <v>-8.332892382961903</v>
       </c>
       <c r="F6">
-        <v>-0.6652454410877348</v>
+        <v>-0.4444681325262077</v>
       </c>
       <c r="G6">
-        <v>-6.707547125968775</v>
+        <v>-5.365756534537849</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.732060034657156</v>
       </c>
       <c r="E7">
-        <v>-11.22482569747428</v>
+        <v>-10.14439519788024</v>
       </c>
       <c r="F7">
-        <v>-0.8413049921439361</v>
+        <v>-0.1762054909666018</v>
       </c>
       <c r="G7">
-        <v>-6.244981150494109</v>
+        <v>-5.022840295943522</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.528741313438797</v>
       </c>
       <c r="E8">
-        <v>-12.5428788136728</v>
+        <v>-10.91067639861417</v>
       </c>
       <c r="F8">
-        <v>-0.6546448234341095</v>
+        <v>-0.4427086801626615</v>
       </c>
       <c r="G8">
-        <v>-6.000520536237707</v>
+        <v>-4.631388149197939</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.357187532663701</v>
       </c>
       <c r="E9">
-        <v>-13.28896302033253</v>
+        <v>-11.59995995579568</v>
       </c>
       <c r="F9">
-        <v>-0.6370569267378704</v>
+        <v>-0.4561514263752919</v>
       </c>
       <c r="G9">
-        <v>-5.492656366149192</v>
+        <v>-4.614117033119562</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.213658902795586</v>
       </c>
       <c r="E10">
-        <v>-14.36302195699778</v>
+        <v>-11.88394056081669</v>
       </c>
       <c r="F10">
-        <v>-0.9791014244974254</v>
+        <v>-0.5404162720576688</v>
       </c>
       <c r="G10">
-        <v>-4.959406932865546</v>
+        <v>-3.99313483249969</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.090304237412692</v>
       </c>
       <c r="E11">
-        <v>-13.75787291840477</v>
+        <v>-13.43325831611294</v>
       </c>
       <c r="F11">
-        <v>-0.8309595116503731</v>
+        <v>-0.6946069236799632</v>
       </c>
       <c r="G11">
-        <v>-4.182216640975164</v>
+        <v>-3.177330337439249</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.98297756624216</v>
       </c>
       <c r="E12">
-        <v>-15.10482222724624</v>
+        <v>-13.14675987954366</v>
       </c>
       <c r="F12">
-        <v>-0.7454338907809352</v>
+        <v>-0.7903247770734461</v>
       </c>
       <c r="G12">
-        <v>-3.974228306924912</v>
+        <v>-3.372006967876091</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.877551777286349</v>
       </c>
       <c r="E13">
-        <v>-15.78652511893891</v>
+        <v>-14.4054265876056</v>
       </c>
       <c r="F13">
-        <v>-0.6460836463261765</v>
+        <v>-0.4415224580418526</v>
       </c>
       <c r="G13">
-        <v>-3.768173331469595</v>
+        <v>-2.170987393866054</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.769502127925706</v>
       </c>
       <c r="E14">
-        <v>-16.59429167005711</v>
+        <v>-15.83520168604736</v>
       </c>
       <c r="F14">
-        <v>-0.8568932099298171</v>
+        <v>-0.3149454337918798</v>
       </c>
       <c r="G14">
-        <v>-3.820834179362782</v>
+        <v>-1.863705867456441</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.644218622123707</v>
       </c>
       <c r="E15">
-        <v>-17.57616898982222</v>
+        <v>-16.24083974528443</v>
       </c>
       <c r="F15">
-        <v>-0.4008471334621885</v>
+        <v>-0.4420791209365339</v>
       </c>
       <c r="G15">
-        <v>-2.806684969407986</v>
+        <v>-1.681410677336473</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.495550651830063</v>
       </c>
       <c r="E16">
-        <v>-18.05689820505448</v>
+        <v>-17.06253588245023</v>
       </c>
       <c r="F16">
-        <v>-0.3539607100963337</v>
+        <v>-0.1639464817725719</v>
       </c>
       <c r="G16">
-        <v>-2.528294573919593</v>
+        <v>-1.301969189807367</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.312116514581761</v>
       </c>
       <c r="E17">
-        <v>-19.2275223214593</v>
+        <v>-17.58219186025243</v>
       </c>
       <c r="F17">
-        <v>-0.2055570331499967</v>
+        <v>-0.1043752683676483</v>
       </c>
       <c r="G17">
-        <v>-2.501300385592375</v>
+        <v>-1.310414391478048</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-7.089485022938932</v>
       </c>
       <c r="E18">
-        <v>-19.87787911607087</v>
+        <v>-18.10587365144744</v>
       </c>
       <c r="F18">
-        <v>0.2571168109074308</v>
+        <v>0.05698573149327864</v>
       </c>
       <c r="G18">
-        <v>-1.698463297409259</v>
+        <v>-0.939401552891926</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.82421760788935</v>
       </c>
       <c r="E19">
-        <v>-20.30554820135526</v>
+        <v>-19.22909370193996</v>
       </c>
       <c r="F19">
-        <v>0.3842297888670149</v>
+        <v>0.1138738628805347</v>
       </c>
       <c r="G19">
-        <v>-1.034146055680328</v>
+        <v>-0.2341361733877493</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.520935767474027</v>
       </c>
       <c r="E20">
-        <v>-21.2282881790542</v>
+        <v>-19.54758580737342</v>
       </c>
       <c r="F20">
-        <v>0.5667804268915532</v>
+        <v>0.5373990634816576</v>
       </c>
       <c r="G20">
-        <v>-1.258700359609093</v>
+        <v>-0.2479941170151385</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.188046593377768</v>
       </c>
       <c r="E21">
-        <v>-22.58768626294276</v>
+        <v>-20.37177260524343</v>
       </c>
       <c r="F21">
-        <v>0.6396709597660901</v>
+        <v>1.04848021345648</v>
       </c>
       <c r="G21">
-        <v>-1.036139004094969</v>
+        <v>-0.1496907777720199</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.839175118111803</v>
       </c>
       <c r="E22">
-        <v>-22.67713721001627</v>
+        <v>-20.82855524992313</v>
       </c>
       <c r="F22">
-        <v>1.164615666594165</v>
+        <v>1.047840713821518</v>
       </c>
       <c r="G22">
-        <v>-1.330956326549226</v>
+        <v>-0.05973994492448249</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.490579969991805</v>
       </c>
       <c r="E23">
-        <v>-21.79579654169546</v>
+        <v>-21.39454657377182</v>
       </c>
       <c r="F23">
-        <v>1.407718305028541</v>
+        <v>1.610946650161761</v>
       </c>
       <c r="G23">
-        <v>-1.082095997271132</v>
+        <v>0.04813087092712987</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.160040035564396</v>
       </c>
       <c r="E24">
-        <v>-23.36828197001494</v>
+        <v>-22.52166564038493</v>
       </c>
       <c r="F24">
-        <v>1.493598467146377</v>
+        <v>1.585689728050404</v>
       </c>
       <c r="G24">
-        <v>-2.197316162539877</v>
+        <v>-0.2672979080546288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.868819163857466</v>
       </c>
       <c r="E25">
-        <v>-23.28999371137034</v>
+        <v>-22.88189216227309</v>
       </c>
       <c r="F25">
-        <v>1.781524065746235</v>
+        <v>1.56699678923883</v>
       </c>
       <c r="G25">
-        <v>-1.139447888193466</v>
+        <v>-0.3285595532588421</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.633875863988124</v>
       </c>
       <c r="E26">
-        <v>-23.63621819162677</v>
+        <v>-22.06417655376004</v>
       </c>
       <c r="F26">
-        <v>1.860001936752655</v>
+        <v>1.776348426213544</v>
       </c>
       <c r="G26">
-        <v>-1.538428215495351</v>
+        <v>-0.759327738828809</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.474374564288009</v>
       </c>
       <c r="E27">
-        <v>-23.05631086715252</v>
+        <v>-22.45469856675951</v>
       </c>
       <c r="F27">
-        <v>1.991132496615816</v>
+        <v>2.234841499989042</v>
       </c>
       <c r="G27">
-        <v>-2.231894810697565</v>
+        <v>-1.083483115852087</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.398976838685329</v>
       </c>
       <c r="E28">
-        <v>-23.54256482067414</v>
+        <v>-22.30876396338832</v>
       </c>
       <c r="F28">
-        <v>2.060481758843385</v>
+        <v>2.290151591473965</v>
       </c>
       <c r="G28">
-        <v>-2.252840632324534</v>
+        <v>-1.526275202820686</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.415855479159939</v>
       </c>
       <c r="E29">
-        <v>-22.94709765950953</v>
+        <v>-22.2090922504795</v>
       </c>
       <c r="F29">
-        <v>2.266064324135361</v>
+        <v>2.089476274676174</v>
       </c>
       <c r="G29">
-        <v>-2.59953420337917</v>
+        <v>-1.600378454171733</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.520562319542054</v>
       </c>
       <c r="E30">
-        <v>-22.78747347921316</v>
+        <v>-22.06979186152955</v>
       </c>
       <c r="F30">
-        <v>2.548917000760475</v>
+        <v>1.996072879806112</v>
       </c>
       <c r="G30">
-        <v>-3.515674712643842</v>
+        <v>-1.902929211005726</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.706829912062908</v>
       </c>
       <c r="E31">
-        <v>-22.85788672155843</v>
+        <v>-21.03346869877022</v>
       </c>
       <c r="F31">
-        <v>2.149257893401408</v>
+        <v>2.564208663016153</v>
       </c>
       <c r="G31">
-        <v>-3.683903394767447</v>
+        <v>-2.224098475952581</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.958380934166415</v>
       </c>
       <c r="E32">
-        <v>-22.60603563962184</v>
+        <v>-20.94221994751566</v>
       </c>
       <c r="F32">
-        <v>2.125069565239663</v>
+        <v>2.149254579931797</v>
       </c>
       <c r="G32">
-        <v>-3.886535266135158</v>
+        <v>-2.900383339805978</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.257599331543122</v>
       </c>
       <c r="E33">
-        <v>-22.24429207894112</v>
+        <v>-21.87891215363224</v>
       </c>
       <c r="F33">
-        <v>2.155242019519232</v>
+        <v>2.195542093665428</v>
       </c>
       <c r="G33">
-        <v>-3.565217026639036</v>
+        <v>-2.768994408443383</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.578852595801717</v>
       </c>
       <c r="E34">
-        <v>-21.90321194515739</v>
+        <v>-21.11485896211008</v>
       </c>
       <c r="F34">
-        <v>2.043607914848359</v>
+        <v>1.94828767780822</v>
       </c>
       <c r="G34">
-        <v>-3.325344828500063</v>
+        <v>-2.734928894844283</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.898395563270211</v>
       </c>
       <c r="E35">
-        <v>-21.32816820176738</v>
+        <v>-20.83215538675923</v>
       </c>
       <c r="F35">
-        <v>2.276346020338909</v>
+        <v>2.269193896183137</v>
       </c>
       <c r="G35">
-        <v>-3.499141848220722</v>
+        <v>-2.455641341514748</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.187321380383389</v>
       </c>
       <c r="E36">
-        <v>-20.85425433991666</v>
+        <v>-20.2266350132976</v>
       </c>
       <c r="F36">
-        <v>2.128112987077548</v>
+        <v>2.307643397551479</v>
       </c>
       <c r="G36">
-        <v>-3.840154523129968</v>
+        <v>-2.600706136500071</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.424431426763506</v>
       </c>
       <c r="E37">
-        <v>-20.25392359766782</v>
+        <v>-19.37121533019668</v>
       </c>
       <c r="F37">
-        <v>1.91082393364921</v>
+        <v>1.986470444872861</v>
       </c>
       <c r="G37">
-        <v>-3.539460982343506</v>
+        <v>-3.284949551829876</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.590288546837788</v>
       </c>
       <c r="E38">
-        <v>-20.83733143255</v>
+        <v>-19.82874517308765</v>
       </c>
       <c r="F38">
-        <v>1.73059272435251</v>
+        <v>2.218562423789226</v>
       </c>
       <c r="G38">
-        <v>-4.459981343356634</v>
+        <v>-2.80934664802156</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.674941480276811</v>
       </c>
       <c r="E39">
-        <v>-20.09928526725389</v>
+        <v>-17.86353236492696</v>
       </c>
       <c r="F39">
-        <v>1.663128826333713</v>
+        <v>2.222192329748294</v>
       </c>
       <c r="G39">
-        <v>-2.858845924924742</v>
+        <v>-2.296834471995909</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.674991105785271</v>
       </c>
       <c r="E40">
-        <v>-18.71988491367346</v>
+        <v>-18.19167464847077</v>
       </c>
       <c r="F40">
-        <v>1.550672981199263</v>
+        <v>1.9636091612904</v>
       </c>
       <c r="G40">
-        <v>-3.477639854943156</v>
+        <v>-2.598594008446017</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.593825798153453</v>
       </c>
       <c r="E41">
-        <v>-19.48104441030471</v>
+        <v>-17.705330125469</v>
       </c>
       <c r="F41">
-        <v>1.678866150252098</v>
+        <v>1.708698973896519</v>
       </c>
       <c r="G41">
-        <v>-3.236794356415638</v>
+        <v>-2.598219916800079</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.443409987517744</v>
       </c>
       <c r="E42">
-        <v>-17.98940582844417</v>
+        <v>-17.68884195160707</v>
       </c>
       <c r="F42">
-        <v>1.50101732560585</v>
+        <v>1.387582350201291</v>
       </c>
       <c r="G42">
-        <v>-2.945088946768296</v>
+        <v>-2.747906233358226</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.237118065845973</v>
       </c>
       <c r="E43">
-        <v>-18.09417660308563</v>
+        <v>-17.16242043363741</v>
       </c>
       <c r="F43">
-        <v>1.340693441733228</v>
+        <v>1.682873791746842</v>
       </c>
       <c r="G43">
-        <v>-3.153583794286056</v>
+        <v>-2.249847899157033</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.994512061596261</v>
       </c>
       <c r="E44">
-        <v>-18.03454112887862</v>
+        <v>-16.99013464001559</v>
       </c>
       <c r="F44">
-        <v>1.423732303659461</v>
+        <v>1.496173033034278</v>
       </c>
       <c r="G44">
-        <v>-3.235764776752924</v>
+        <v>-1.359979879292016</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.732407728669727</v>
       </c>
       <c r="E45">
-        <v>-17.21154984814663</v>
+        <v>-15.25582872150602</v>
       </c>
       <c r="F45">
-        <v>1.267558540474865</v>
+        <v>1.573403382732082</v>
       </c>
       <c r="G45">
-        <v>-2.349713815894687</v>
+        <v>-1.316330336356726</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.470346488197635</v>
       </c>
       <c r="E46">
-        <v>-16.86690127684486</v>
+        <v>-14.92470670206516</v>
       </c>
       <c r="F46">
-        <v>1.402224572413175</v>
+        <v>1.381061442006453</v>
       </c>
       <c r="G46">
-        <v>-3.060070814438263</v>
+        <v>-1.392416604485795</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.222552162834773</v>
       </c>
       <c r="E47">
-        <v>-16.28372439413707</v>
+        <v>-15.36402302249728</v>
       </c>
       <c r="F47">
-        <v>1.039522248362606</v>
+        <v>1.136138052020723</v>
       </c>
       <c r="G47">
-        <v>-2.342520000437851</v>
+        <v>-2.251195291191516</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.00198575933832</v>
       </c>
       <c r="E48">
-        <v>-14.84870079432042</v>
+        <v>-14.054972512626</v>
       </c>
       <c r="F48">
-        <v>1.037146490651377</v>
+        <v>1.150129177454007</v>
       </c>
       <c r="G48">
-        <v>-2.43937001018923</v>
+        <v>-2.084863551661914</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.814377658627329</v>
       </c>
       <c r="E49">
-        <v>-15.04942993318442</v>
+        <v>-13.81732272517747</v>
       </c>
       <c r="F49">
-        <v>1.129277513190738</v>
+        <v>1.156792564842126</v>
       </c>
       <c r="G49">
-        <v>-2.364866182827932</v>
+        <v>-1.27006877299095</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.662269464833316</v>
       </c>
       <c r="E50">
-        <v>-14.73773053876246</v>
+        <v>-13.66051978418787</v>
       </c>
       <c r="F50">
-        <v>1.064364986772563</v>
+        <v>1.082113586744945</v>
       </c>
       <c r="G50">
-        <v>-2.749458879216144</v>
+        <v>-1.562456155019381</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.542839629350525</v>
       </c>
       <c r="E51">
-        <v>-15.08949334273028</v>
+        <v>-12.17288890182411</v>
       </c>
       <c r="F51">
-        <v>0.9696875628369963</v>
+        <v>1.098485440093875</v>
       </c>
       <c r="G51">
-        <v>-2.259878852141024</v>
+        <v>-1.903528419748334</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.451100984694089</v>
       </c>
       <c r="E52">
-        <v>-13.32902642987839</v>
+        <v>-12.39417731268293</v>
       </c>
       <c r="F52">
-        <v>0.889163624345662</v>
+        <v>0.6749063956115698</v>
       </c>
       <c r="G52">
-        <v>-2.753961221149553</v>
+        <v>-2.09492098901022</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.381064663106497</v>
       </c>
       <c r="E53">
-        <v>-13.37412550252077</v>
+        <v>-12.21835478086112</v>
       </c>
       <c r="F53">
-        <v>0.7921667716822567</v>
+        <v>0.982215791436936</v>
       </c>
       <c r="G53">
-        <v>-3.086743879848171</v>
+        <v>-1.675762886646477</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.324959732267798</v>
       </c>
       <c r="E54">
-        <v>-12.83490198853143</v>
+        <v>-11.36460610466904</v>
       </c>
       <c r="F54">
-        <v>0.5791338699695022</v>
+        <v>1.150803468519886</v>
       </c>
       <c r="G54">
-        <v>-3.782246460557037</v>
+        <v>-2.753365322952484</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.279896781065324</v>
       </c>
       <c r="E55">
-        <v>-12.99665002313741</v>
+        <v>-11.23347055435492</v>
       </c>
       <c r="F55">
-        <v>0.8658997542054406</v>
+        <v>0.9755822252753176</v>
       </c>
       <c r="G55">
-        <v>-3.261428125773354</v>
+        <v>-2.636532860326064</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.240560863889045</v>
       </c>
       <c r="E56">
-        <v>-11.89975399205148</v>
+        <v>-10.66118012316157</v>
       </c>
       <c r="F56">
-        <v>0.6989920062153683</v>
+        <v>0.8630352597265599</v>
       </c>
       <c r="G56">
-        <v>-3.956725452658786</v>
+        <v>-2.692097056657192</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.208467217036456</v>
       </c>
       <c r="E57">
-        <v>-12.66096783037082</v>
+        <v>-11.1066415828221</v>
       </c>
       <c r="F57">
-        <v>0.4947290301960522</v>
+        <v>0.7420174091167746</v>
       </c>
       <c r="G57">
-        <v>-4.530989234628461</v>
+        <v>-3.318839606515395</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.181918469072058</v>
       </c>
       <c r="E58">
-        <v>-11.66829010009742</v>
+        <v>-9.826840486566361</v>
       </c>
       <c r="F58">
-        <v>0.9006630206313248</v>
+        <v>0.6708034918655039</v>
       </c>
       <c r="G58">
-        <v>-4.050864125613501</v>
+        <v>-3.355242365265221</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.164271099511789</v>
       </c>
       <c r="E59">
-        <v>-11.83563532857687</v>
+        <v>-10.52470550199241</v>
       </c>
       <c r="F59">
-        <v>0.5503779239487202</v>
+        <v>0.890870061195429</v>
       </c>
       <c r="G59">
-        <v>-4.388423901525288</v>
+        <v>-4.093192760878622</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.156060928992782</v>
       </c>
       <c r="E60">
-        <v>-11.44552993518611</v>
+        <v>-8.996843656544508</v>
       </c>
       <c r="F60">
-        <v>0.603998974299335</v>
+        <v>0.7793751222482267</v>
       </c>
       <c r="G60">
-        <v>-4.519905528162982</v>
+        <v>-3.956745315932021</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.160937530170236</v>
       </c>
       <c r="E61">
-        <v>-11.82300994304349</v>
+        <v>-9.673542584458705</v>
       </c>
       <c r="F61">
-        <v>0.2817971893064393</v>
+        <v>1.227631231659929</v>
       </c>
       <c r="G61">
-        <v>-5.481592522956948</v>
+        <v>-4.718796483071316</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.179307433279451</v>
       </c>
       <c r="E62">
-        <v>-10.40762180652409</v>
+        <v>-8.760987144803012</v>
       </c>
       <c r="F62">
-        <v>0.3250048330364615</v>
+        <v>0.9783307483178063</v>
       </c>
       <c r="G62">
-        <v>-5.299545623752425</v>
+        <v>-4.378296942720657</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.213503639284918</v>
       </c>
       <c r="E63">
-        <v>-10.62697655898164</v>
+        <v>-8.933318223164909</v>
       </c>
       <c r="F63">
-        <v>0.3874032643871398</v>
+        <v>0.4818694546349926</v>
       </c>
       <c r="G63">
-        <v>-5.973996445377066</v>
+        <v>-4.885369892425286</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.260969116407461</v>
       </c>
       <c r="E64">
-        <v>-9.982792074442514</v>
+        <v>-9.115136454572873</v>
       </c>
       <c r="F64">
-        <v>0.2941324083015267</v>
+        <v>0.8560338984380985</v>
       </c>
       <c r="G64">
-        <v>-6.036747836073951</v>
+        <v>-5.323239198176989</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.321479540898754</v>
       </c>
       <c r="E65">
-        <v>-10.38080418345067</v>
+        <v>-8.03101977713659</v>
       </c>
       <c r="F65">
-        <v>0.2691852955988168</v>
+        <v>0.8469069463940536</v>
       </c>
       <c r="G65">
-        <v>-6.625796514422013</v>
+        <v>-5.188390746725855</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.390039670221772</v>
       </c>
       <c r="E66">
-        <v>-10.74414176698209</v>
+        <v>-8.818992368367262</v>
       </c>
       <c r="F66">
-        <v>0.3728654164680085</v>
+        <v>0.5215366560854497</v>
       </c>
       <c r="G66">
-        <v>-6.620142102640937</v>
+        <v>-5.83302348467828</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.46387025739958</v>
       </c>
       <c r="E67">
-        <v>-10.61253978384518</v>
+        <v>-8.280434540057049</v>
       </c>
       <c r="F67">
-        <v>0.07132808470534928</v>
+        <v>0.3329248537746275</v>
       </c>
       <c r="G67">
-        <v>-6.344866930504999</v>
+        <v>-5.652390188419027</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.537837508227606</v>
       </c>
       <c r="E68">
-        <v>-9.690877582960066</v>
+        <v>-8.374952849545146</v>
       </c>
       <c r="F68">
-        <v>-0.06003027619358232</v>
+        <v>0.6224061263569428</v>
       </c>
       <c r="G68">
-        <v>-6.580587704537725</v>
+        <v>-5.537203066925625</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.607588394640026</v>
       </c>
       <c r="E69">
-        <v>-10.45008077882001</v>
+        <v>-8.563246798784078</v>
       </c>
       <c r="F69">
-        <v>-0.111222553319189</v>
+        <v>0.4049132945475158</v>
       </c>
       <c r="G69">
-        <v>-6.584941071921866</v>
+        <v>-5.927443554003834</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.670141273647957</v>
       </c>
       <c r="E70">
-        <v>-10.86007975852647</v>
+        <v>-8.777701742365323</v>
       </c>
       <c r="F70">
-        <v>-0.1358913345745582</v>
+        <v>0.1591383428717081</v>
       </c>
       <c r="G70">
-        <v>-7.231527031742462</v>
+        <v>-6.301849701767709</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.72139138916913</v>
       </c>
       <c r="E71">
-        <v>-10.41927809861984</v>
+        <v>-8.423176569252828</v>
       </c>
       <c r="F71">
-        <v>-0.1814672807091842</v>
+        <v>0.2567266498607123</v>
       </c>
       <c r="G71">
-        <v>-6.711572749344529</v>
+        <v>-5.775592140663004</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.761066529188841</v>
       </c>
       <c r="E72">
-        <v>-10.22072715575353</v>
+        <v>-8.153084794013344</v>
       </c>
       <c r="F72">
-        <v>0.1118186833541891</v>
+        <v>0.2155253119802704</v>
       </c>
       <c r="G72">
-        <v>-7.42335990356107</v>
+        <v>-5.918313069406524</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.786889223694689</v>
       </c>
       <c r="E73">
-        <v>-9.489691068221296</v>
+        <v>-8.882535915642894</v>
       </c>
       <c r="F73">
-        <v>-0.1312019467073103</v>
+        <v>0.1910478835949478</v>
       </c>
       <c r="G73">
-        <v>-6.91574733493354</v>
+        <v>-5.161969282776933</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.799772897431043</v>
       </c>
       <c r="E74">
-        <v>-10.97998922177557</v>
+        <v>-8.678745528349712</v>
       </c>
       <c r="F74">
-        <v>-0.2520151905686042</v>
+        <v>-0.08413659598245074</v>
       </c>
       <c r="G74">
-        <v>-7.086488721121452</v>
+        <v>-5.525351313895034</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.798063866277007</v>
       </c>
       <c r="E75">
-        <v>-11.18987493508308</v>
+        <v>-8.776791519089782</v>
       </c>
       <c r="F75">
-        <v>0.001278023655011885</v>
+        <v>0.1304751740000396</v>
       </c>
       <c r="G75">
-        <v>-6.257336106446669</v>
+        <v>-6.04274654459111</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.781429554369851</v>
       </c>
       <c r="E76">
-        <v>-11.02999263176827</v>
+        <v>-8.864195595911829</v>
       </c>
       <c r="F76">
-        <v>-0.3140557672012731</v>
+        <v>0.04607281932879795</v>
       </c>
       <c r="G76">
-        <v>-6.074206658850804</v>
+        <v>-5.657822793648971</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.746464670185404</v>
       </c>
       <c r="E77">
-        <v>-11.66220383103111</v>
+        <v>-9.902855451259116</v>
       </c>
       <c r="F77">
-        <v>-0.3955911422914257</v>
+        <v>-0.1516816740067224</v>
       </c>
       <c r="G77">
-        <v>-5.835605710198912</v>
+        <v>-5.212885473170923</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.690942237008663</v>
       </c>
       <c r="E78">
-        <v>-11.78386581372118</v>
+        <v>-10.04112787660932</v>
       </c>
       <c r="F78">
-        <v>-0.1115414747692668</v>
+        <v>-0.1924456338984861</v>
       </c>
       <c r="G78">
-        <v>-5.784527303073497</v>
+        <v>-5.130065555414976</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.610885015802393</v>
       </c>
       <c r="E79">
-        <v>-12.28596942626965</v>
+        <v>-10.20885349690542</v>
       </c>
       <c r="F79">
-        <v>-0.08163658316080183</v>
+        <v>-0.329599253147403</v>
       </c>
       <c r="G79">
-        <v>-5.905103992704832</v>
+        <v>-5.320445097741844</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.504163582359337</v>
       </c>
       <c r="E80">
-        <v>-12.38109002280077</v>
+        <v>-11.86905999522749</v>
       </c>
       <c r="F80">
-        <v>-0.5407327084055382</v>
+        <v>-0.03307520090648641</v>
       </c>
       <c r="G80">
-        <v>-6.262821680405241</v>
+        <v>-5.164018510465741</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.370107947609906</v>
       </c>
       <c r="E81">
-        <v>-14.42498053837072</v>
+        <v>-11.21712276318723</v>
       </c>
       <c r="F81">
-        <v>-0.3517423421916366</v>
+        <v>-0.3787421493184837</v>
       </c>
       <c r="G81">
-        <v>-5.828180156554327</v>
+        <v>-4.934700331505965</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.209695676872688</v>
       </c>
       <c r="E82">
-        <v>-14.39742024556004</v>
+        <v>-12.33156210257888</v>
       </c>
       <c r="F82">
-        <v>-0.1773602351261043</v>
+        <v>0.1062967862471276</v>
       </c>
       <c r="G82">
-        <v>-5.420708279944211</v>
+        <v>-5.064837876654716</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.028313974937892</v>
       </c>
       <c r="E83">
-        <v>-15.139514866619</v>
+        <v>-13.21563344072632</v>
       </c>
       <c r="F83">
-        <v>-0.8911122389720619</v>
+        <v>-0.3167371924841351</v>
       </c>
       <c r="G83">
-        <v>-5.977965789478652</v>
+        <v>-4.69565908029735</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.830461146251297</v>
       </c>
       <c r="E84">
-        <v>-16.15552329497993</v>
+        <v>-14.64070345467411</v>
       </c>
       <c r="F84">
-        <v>-0.6613330618443126</v>
+        <v>-0.4855037969260896</v>
       </c>
       <c r="G84">
-        <v>-4.836231464985883</v>
+        <v>-3.719829434959618</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.626834869682613</v>
       </c>
       <c r="E85">
-        <v>-16.55593549521215</v>
+        <v>-15.66656131400172</v>
       </c>
       <c r="F85">
-        <v>-0.8022872307372737</v>
+        <v>-0.5939155524000721</v>
       </c>
       <c r="G85">
-        <v>-5.535299503240544</v>
+        <v>-4.322140158738</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.424628353461103</v>
       </c>
       <c r="E86">
-        <v>-18.43958142954668</v>
+        <v>-17.43141178969303</v>
       </c>
       <c r="F86">
-        <v>-0.814461746456218</v>
+        <v>-0.6434767741095665</v>
       </c>
       <c r="G86">
-        <v>-5.423171325825429</v>
+        <v>-3.639614916543077</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.236070239337848</v>
       </c>
       <c r="E87">
-        <v>-19.18146321232728</v>
+        <v>-17.44145594504204</v>
       </c>
       <c r="F87">
-        <v>-0.6627064949981543</v>
+        <v>-0.3153438785126264</v>
       </c>
       <c r="G87">
-        <v>-4.396875724287047</v>
+        <v>-4.744857097556459</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.06862048732698</v>
       </c>
       <c r="E88">
-        <v>-20.24115330096619</v>
+        <v>-19.49664047478713</v>
       </c>
       <c r="F88">
-        <v>-0.8456033905970627</v>
+        <v>-0.3576428032017775</v>
       </c>
       <c r="G88">
-        <v>-4.207787294720495</v>
+        <v>-3.129635307854969</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.93132860978288</v>
       </c>
       <c r="E89">
-        <v>-22.72966298003124</v>
+        <v>-20.94037685859454</v>
       </c>
       <c r="F89">
-        <v>-0.924755552669361</v>
+        <v>-0.6229291206831248</v>
       </c>
       <c r="G89">
-        <v>-4.552818971914416</v>
+        <v>-3.278096722563585</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.828277742450019</v>
       </c>
       <c r="E90">
-        <v>-23.39154474099234</v>
+        <v>-22.69380652283851</v>
       </c>
       <c r="F90">
-        <v>-0.8658950784960394</v>
+        <v>-0.9270418467010877</v>
       </c>
       <c r="G90">
-        <v>-4.207068906338472</v>
+        <v>-3.565044878270994</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.762478720258339</v>
       </c>
       <c r="E91">
-        <v>-25.24949158533335</v>
+        <v>-24.01576318363165</v>
       </c>
       <c r="F91">
-        <v>-1.115384429606</v>
+        <v>-0.7965980034148468</v>
       </c>
       <c r="G91">
-        <v>-4.727142368375819</v>
+        <v>-4.738749141036504</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.731574034825663</v>
       </c>
       <c r="E92">
-        <v>-26.77772929412388</v>
+        <v>-26.32168479070743</v>
       </c>
       <c r="F92">
-        <v>-1.328167992730512</v>
+        <v>-0.9715318031706435</v>
       </c>
       <c r="G92">
-        <v>-4.814795682619102</v>
+        <v>-3.959466584365302</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.732635101519281</v>
       </c>
       <c r="E93">
-        <v>-28.79831628245037</v>
+        <v>-28.04744095029053</v>
       </c>
       <c r="F93">
-        <v>-1.101343602128549</v>
+        <v>-0.6753043064599291</v>
       </c>
       <c r="G93">
-        <v>-5.36679273529164</v>
+        <v>-4.19381679254477</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.758954360978162</v>
       </c>
       <c r="E94">
-        <v>-30.54215463874609</v>
+        <v>-29.25315168330677</v>
       </c>
       <c r="F94">
-        <v>-1.375579601029742</v>
+        <v>-1.016696050706078</v>
       </c>
       <c r="G94">
-        <v>-4.84651401943086</v>
+        <v>-4.303462060805431</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.805079667238454</v>
       </c>
       <c r="E95">
-        <v>-33.0412677397001</v>
+        <v>-32.42955694226998</v>
       </c>
       <c r="F95">
-        <v>-1.432839669380854</v>
+        <v>-1.202086332187413</v>
       </c>
       <c r="G95">
-        <v>-5.581849084068236</v>
+        <v>-5.005291094039845</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.868202825286851</v>
       </c>
       <c r="E96">
-        <v>-34.6024251902894</v>
+        <v>-35.20481865244874</v>
       </c>
       <c r="F96">
-        <v>-1.291420786374923</v>
+        <v>-1.287260725278064</v>
       </c>
       <c r="G96">
-        <v>-5.841299848526458</v>
+        <v>-4.588172287728293</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.942445614060847</v>
       </c>
       <c r="E97">
-        <v>-37.27267385246729</v>
+        <v>-37.01719772708756</v>
       </c>
       <c r="F97">
-        <v>-1.60933245658872</v>
+        <v>-1.65384146550854</v>
       </c>
       <c r="G97">
-        <v>-5.972990039533127</v>
+        <v>-4.602748619737704</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.036274870656598</v>
       </c>
       <c r="E98">
-        <v>-40.01937221284266</v>
+        <v>-40.05059377688854</v>
       </c>
       <c r="F98">
-        <v>-1.868030768115603</v>
+        <v>-1.283445265020769</v>
       </c>
       <c r="G98">
-        <v>-5.846192834833501</v>
+        <v>-5.358311117620028</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.142046094821235</v>
       </c>
       <c r="E99">
-        <v>-42.539932166697</v>
+        <v>-43.02254749135346</v>
       </c>
       <c r="F99">
-        <v>-1.919324934431754</v>
+        <v>-1.469359074700674</v>
       </c>
       <c r="G99">
-        <v>-6.700207646508211</v>
+        <v>-5.548091451204288</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.284258862400444</v>
       </c>
       <c r="E100">
-        <v>-44.35104553285068</v>
+        <v>-45.28932270486993</v>
       </c>
       <c r="F100">
-        <v>-1.927862088885006</v>
+        <v>-1.495111360518905</v>
       </c>
       <c r="G100">
-        <v>-6.6529231245708</v>
+        <v>-4.958681923392446</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.440351370083804</v>
       </c>
       <c r="E101">
-        <v>-46.52944757610747</v>
+        <v>-47.24699786804486</v>
       </c>
       <c r="F101">
-        <v>-2.335106556551507</v>
+        <v>-1.802755416775002</v>
       </c>
       <c r="G101">
-        <v>-6.709454000199395</v>
+        <v>-5.879304911317291</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.662780663863623</v>
       </c>
       <c r="E102">
-        <v>-48.96040714324604</v>
+        <v>-49.5125673753568</v>
       </c>
       <c r="F102">
-        <v>-2.554362982561494</v>
+        <v>-2.264071566659241</v>
       </c>
       <c r="G102">
-        <v>-6.870425966500918</v>
+        <v>-6.154457593268277</v>
       </c>
     </row>
   </sheetData>
